--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-diagnostico-ges.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-diagnostico-ges.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/StructureDefinition/diagnostico-ges</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/StructureDefinition/diagnostico-ges</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:36:45-03:00</t>
+    <t>2026-09-24T11:47:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -319,7 +319,7 @@
 </t>
   </si>
   <si>
-    <t>identifies the meaning of the extension</t>
+    <t>URL que identifica la extensión</t>
   </si>
   <si>
     <t>Source of the definition for the extension code - a logical name or a URL.</t>
@@ -338,7 +338,7 @@
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
+    <t>true si el diagnóstico es GES</t>
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>

--- a/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-diagnostico-ges.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/StructureDefinition-diagnostico-ges.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
